--- a/ValenciaGoez_WilfranCamilo_Montecarlo_Simulacion.xlsx
+++ b/ValenciaGoez_WilfranCamilo_Montecarlo_Simulacion.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>[Nombre y Apellido del Estudiante]</t>
+          <t>Wilfran Camilo Valencia Goez</t>
         </is>
       </c>
     </row>
